--- a/jogos_2025-02-20.xlsx
+++ b/jogos_2025-02-20.xlsx
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="T4" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.75</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.27</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.9</v>
+        <v>3.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>['14', '24', '30', '40', '51', '62', '80']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
       <c r="AG4" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.46</v>
+        <v>2.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45708.41666666666</v>
@@ -1030,109 +1030,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S5" t="n">
         <v>1.95</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>3.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.55</v>
+        <v>6.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['14', '24', '30', '40', '51', '62', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.9</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45708.41666666666</v>
